--- a/reports/pdf_rolling5_20260803.xlsx
+++ b/reports/pdf_rolling5_20260803.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-27 ~ 2026-08-03  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-27 ~ 2026-08-03  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1253,468 +1253,539 @@
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="19" t="n"/>
-      <c r="H24" s="19" t="n"/>
-      <c r="I24" s="19" t="n"/>
-      <c r="J24" s="19" t="n"/>
-      <c r="K24" s="19" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="19" t="n"/>
-      <c r="F26" s="19" t="n"/>
-      <c r="G26" s="19" t="n"/>
-      <c r="H26" s="19" t="n"/>
-      <c r="I26" s="19" t="n"/>
-      <c r="J26" s="19" t="n"/>
-      <c r="K26" s="19" t="n"/>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 212억   ·   현금 14억(6.5%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 8종목  /  매도 7종목</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,812억   ·   현금 80억(3.7%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>398634600</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>0.17%→0.37%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>25→51</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>코미코  (편출)</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-4633244000</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>2.05%→0.00%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>110→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>4655882000</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>2.74%→5.22%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>30→52</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>-1872780000</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>5.79%→5.03%</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>140→119</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>1188152000</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>3.05%→3.95%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>24→28</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>-597849000</v>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>5.57%→4.98%</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>130→123</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>75322800</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>3.17%→2.78%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>230→233</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>에코프로</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-162787800</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>2.61%→2.75%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>110→107</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,799억   ·   현금 35억(1.8%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>심텍홀딩스</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>12321880</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>0.46%→0.54%</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>485→547</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>코미코  (편출)</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>-152</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>-628428800</v>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>3.01%→0.00%</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>152→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>57870960</v>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>3.25%→3.64%</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>573→622</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>-145</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>-35319100</v>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>3.03%→2.96%</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>2,597→2,452</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="n">
-        <v>33</v>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>69973200</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>6.78%→7.36%</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>667→700</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>금양그린파워</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>-91</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>-44884840</v>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>1.10%→0.92%</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>466→375</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="C34" s="11" t="n">
-        <v>47241600</v>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>2.25%→2.56%</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>278→306</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>-27785600</v>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>0.63%→0.52%</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>38→30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
-        <v>15</v>
+        <v>264</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>57684000</v>
+        <v>5907792000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>3.10%→3.49%</t>
+          <t>4.07%→7.13%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>168→183</t>
+          <t>340→604</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오  (편출)</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-7</v>
+        <v>-83</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-41442800</v>
+        <v>-2635914000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.00%</t>
+          <t>7.46%→5.51%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>7→0</t>
+          <t>412→329</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>20846800</v>
+        <v>2626869000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>0.75%→0.88%</t>
+          <t>9.67%→12.24%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>98→111</t>
+          <t>329→371</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-6</v>
+        <v>-68</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-103512000</v>
+        <v>-1993250000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>1.99%→1.54%</t>
+          <t>5.85%→4.64%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>24→18</t>
+          <t>368→300</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>43304800</v>
+        <v>2170297500</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>1.61%→1.87%</t>
+          <t>11.93%→14.23%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>85→96</t>
+          <t>240→261</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-6</v>
+        <v>-35</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-127452000</v>
+        <v>-3910287500</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2.04%→1.47%</t>
+          <t>7.78%→5.01%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>20→14</t>
+          <t>120→85</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>30825600</v>
+        <v>185724000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.90%</t>
+          <t>3.95%→3.67%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>72→76</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="n"/>
-      <c r="H38" s="17" t="n"/>
-      <c r="I38" s="17" t="n"/>
-      <c r="J38" s="17" t="n"/>
-      <c r="K38" s="17" t="n"/>
+          <t>401→412</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>삼성바이오로직스</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>-3482325000</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>10.05%→8.66%</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>40→33</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 418억   ·   현금 25억(5.5%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 4종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 212억   ·   현금 14억(6.5%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 8종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1803,215 +1874,644 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>심텍홀딩스</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>505512000</v>
+        <v>12321880</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>5.12%→5.38%</t>
+          <t>0.46%→0.54%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>184→235</t>
+          <t>485→547</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>리센스메디컬  (편출)</t>
+          <t>코미코  (편출)</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-607</v>
+        <v>-152</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-749183680</v>
+        <v>-628428800</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>1.59%→0.00%</t>
+          <t>3.01%→0.00%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>607→0</t>
+          <t>152→0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>펩트론</t>
+          <t>에프앤가이드</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>143136000</v>
+        <v>57870960</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>1.67%→2.38%</t>
+          <t>3.25%→3.64%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>62→72</t>
+          <t>573→622</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>큐라클</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-518</v>
+        <v>-145</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-477471680</v>
+        <v>-35319100</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>1.32%→0.21%</t>
+          <t>3.03%→2.96%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>617→99</t>
+          <t>2,597→2,452</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>234360000</v>
+        <v>69973200</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>4.47%→5.35%</t>
+          <t>6.78%→7.36%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>80→89</t>
+          <t>667→700</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>금양그린파워</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-33</v>
+        <v>-91</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-690043200</v>
+        <v>-44884840</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>9.52%→9.27%</t>
+          <t>1.10%→0.92%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>225→192</t>
+          <t>466→375</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>47241600</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>2.25%→2.56%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>278→306</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-27785600</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>0.63%→0.52%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>38→30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>57684000</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>3.10%→3.49%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>168→183</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오  (편출)</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-41442800</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>0.20%→0.00%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>7→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>알멕</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>20846800</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>0.75%→0.88%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>98→111</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-103512000</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>1.99%→1.54%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>24→18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>43304800</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>1.61%→1.87%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>85→96</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-127452000</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>2.04%→1.47%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>20→14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>30825600</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>2.66%→2.90%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>72→76</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="n"/>
+      <c r="H50" s="17" t="n"/>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="17" t="n"/>
+      <c r="K50" s="17" t="n"/>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 418억   ·   현금 25억(5.5%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>505512000</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>5.12%→5.38%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>184→235</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>리센스메디컬  (편출)</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-607</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-749183680</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>1.59%→0.00%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>607→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>펩트론</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>143136000</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>1.67%→2.38%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>62→72</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>큐라클</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-518</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-477471680</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>1.32%→0.21%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>617→99</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>234360000</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>4.47%→5.35%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>80→89</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-690043200</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>9.52%→9.27%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>225→192</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n">
+      <c r="B58" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="11" t="n">
+      <c r="C58" s="11" t="n">
         <v>665280000</v>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>1.09%→2.69%</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>3→7</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="H46" s="15" t="n">
+      <c r="H58" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I46" s="15" t="n">
+      <c r="I58" s="15" t="n">
         <v>-310968000</v>
       </c>
-      <c r="J46" s="16" t="inlineStr">
+      <c r="J58" s="16" t="inlineStr">
         <is>
           <t>9.74%→10.13%</t>
         </is>
       </c>
-      <c r="K46" s="13" t="inlineStr">
+      <c r="K58" s="13" t="inlineStr">
         <is>
           <t>136→127</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B48" s="19" t="n"/>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
-      <c r="G48" s="19" t="n"/>
-      <c r="H48" s="19" t="n"/>
-      <c r="I48" s="19" t="n"/>
-      <c r="J48" s="19" t="n"/>
-      <c r="K48" s="19" t="n"/>
+      <c r="B60" s="19" t="n"/>
+      <c r="C60" s="19" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="19" t="n"/>
+      <c r="G60" s="19" t="n"/>
+      <c r="H60" s="19" t="n"/>
+      <c r="I60" s="19" t="n"/>
+      <c r="J60" s="19" t="n"/>
+      <c r="K60" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="21">
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="G53:K53"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="G29:K29"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="A52:K52"/>
     <mergeCell ref="G41:K41"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A40:K40"/>
-    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260803.xlsx
+++ b/reports/pdf_rolling5_20260803.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,286억   ·   현금 255억(6.4%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 11종목  /  매도 8종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,907억   ·   현금 257억(6.4%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 11종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>395262240</v>
+        <v>399203040</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-171</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-10530898200</v>
+        <v>-10635892200</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>61</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1615231200</v>
+        <v>1631335200</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-59</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-3751821800</v>
+        <v>-3789227800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>52</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1908909600</v>
+        <v>1927941600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-36</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-674858520</v>
+        <v>-681586920</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>404168880</v>
+        <v>408198480</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-35</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-491470000</v>
+        <v>-496370000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2004796400</v>
+        <v>2024784400</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-31</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-883041200</v>
+        <v>-891845200</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>774516600</v>
+        <v>782238600</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-27</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2567278800</v>
+        <v>-2592874800</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>518551000</v>
+        <v>523721000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-19</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-756562900</v>
+        <v>-764105900</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>746081550</v>
+        <v>753520050</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-6</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2605794000</v>
+        <v>-2631774000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1330379200</v>
+        <v>1343643200</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>385452900</v>
+        <v>389295900</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>921757000</v>
+        <v>930947000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,004억   ·   현금 27억(0.8%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 1종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,202억   ·   현금 27억(0.8%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1255,7 +1255,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,812억   ·   현금 80억(3.7%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,154억   ·   현금 80억(3.7%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1351,7 +1351,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>398634600</v>
+        <v>398053500</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>-110</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-4633244000</v>
+        <v>-4626490000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>22</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>4655882000</v>
+        <v>4649095000</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>-21</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1872780000</v>
+        <v>-1870050000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1188152000</v>
+        <v>1186420000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>-7</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-597849000</v>
+        <v>-596977500</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>75322800</v>
+        <v>75213000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-162787800</v>
+        <v>-162550500</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,799억   ·   현금 35억(1.8%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,919억   ·   현금 35억(1.8%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1785,7 +1785,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 212억   ·   현금 14억(6.5%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 8종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 241억   ·   현금 14억(5.6%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 8종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1881,7 +1881,7 @@
         <v>62</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>12321880</v>
+        <v>14608440</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1902,11 +1902,11 @@
         <v>-152</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-628428800</v>
+        <v>-636697600</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>3.01%→0.00%</t>
+          <t>2.58%→0.00%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -1925,11 +1925,11 @@
         <v>49</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>57870960</v>
+        <v>62480880</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>3.25%→3.64%</t>
+          <t>2.97%→3.31%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1946,11 +1946,11 @@
         <v>-145</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-35319100</v>
+        <v>-38965850</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>3.03%→2.96%</t>
+          <t>2.83%→2.75%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -1969,11 +1969,11 @@
         <v>33</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>69973200</v>
+        <v>83853000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>6.78%→7.36%</t>
+          <t>6.88%→7.41%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1990,11 +1990,11 @@
         <v>-91</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-44884840</v>
+        <v>-49049000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>1.10%→0.92%</t>
+          <t>1.02%→0.84%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -2013,11 +2013,11 @@
         <v>28</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>47241600</v>
+        <v>59505600</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.25%→2.56%</t>
+          <t>2.40%→2.71%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2034,11 +2034,11 @@
         <v>-8</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-27785600</v>
+        <v>-31046400</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.52%</t>
+          <t>0.60%→0.49%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2057,11 +2057,11 @@
         <v>15</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>57684000</v>
+        <v>75652500</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>3.10%→3.49%</t>
+          <t>3.44%→3.85%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2078,11 +2078,11 @@
         <v>-7</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-41442800</v>
+        <v>-47162500</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.00%</t>
+          <t>0.19%→0.00%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2101,11 +2101,11 @@
         <v>13</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>20846800</v>
+        <v>23523500</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>0.75%→0.88%</t>
+          <t>0.72%→0.84%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2115,23 +2115,23 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-103512000</v>
+        <v>-142527000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.99%→1.54%</t>
+          <t>1.93%→1.39%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>24→18</t>
+          <t>20→14</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>11</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>43304800</v>
+        <v>54292700</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>1.61%→1.87%</t>
+          <t>1.70%→1.97%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2159,23 +2159,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-127452000</v>
+        <v>-117810000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2.04%→1.47%</t>
+          <t>1.91%→1.47%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>20→14</t>
+          <t>24→18</t>
         </is>
       </c>
     </row>
@@ -2189,11 +2189,11 @@
         <v>4</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>30825600</v>
+        <v>39916800</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.90%</t>
+          <t>2.92%→3.16%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 418억   ·   현금 25억(5.5%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 4종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 446억   ·   현금 25억(5.5%)      오늘 2026-08-03  vs  5일전 2026-07-27      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B52" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260803.xlsx
+++ b/reports/pdf_rolling5_20260803.xlsx
@@ -2115,23 +2115,23 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-142527000</v>
+        <v>-117810000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.93%→1.39%</t>
+          <t>1.91%→1.47%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>20→14</t>
+          <t>24→18</t>
         </is>
       </c>
     </row>
@@ -2159,23 +2159,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-117810000</v>
+        <v>-142527000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.91%→1.47%</t>
+          <t>1.93%→1.39%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>24→18</t>
+          <t>20→14</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260803.xlsx
+++ b/reports/pdf_rolling5_20260803.xlsx
@@ -2115,23 +2115,23 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-117810000</v>
+        <v>-142527000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.91%→1.47%</t>
+          <t>1.93%→1.39%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>24→18</t>
+          <t>20→14</t>
         </is>
       </c>
     </row>
@@ -2159,23 +2159,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-142527000</v>
+        <v>-117810000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.93%→1.39%</t>
+          <t>1.91%→1.47%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>20→14</t>
+          <t>24→18</t>
         </is>
       </c>
     </row>
